--- a/ig/DM-MARS-2026/CodeSystem-condition-ver-status-supplement-fr.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-condition-ver-status-supplement-fr.xlsx
@@ -105,7 +105,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/condition-ver-status|2.0.1</t>
+    <t>http://terminology.hl7.org/CodeSystem/condition-ver-status|4.0.1</t>
   </si>
   <si>
     <t>Count</t>
